--- a/01需求矩阵-第4组-徐钲.xlsx
+++ b/01需求矩阵-第4组-徐钲.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AAAnaughty rabbit\course\大三上\实训\课程用资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AAAnaughty rabbit\course\大三上\实训\Gale-Verdict-software-developing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3853F2D1-4B21-40DD-BC77-67C6B4FD177F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CBB91F-011D-49EA-9241-3D5F935ED857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,22 +92,7 @@
     <author>Blueberry</author>
   </authors>
   <commentList>
-    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{2DF144BB-2480-4B5B-AACA-05A71939FD8C}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F19" authorId="0" shapeId="0" xr:uid="{039450CA-A635-4299-BC53-1E5E55EEDDF3}">
+    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{039450CA-A635-4299-BC53-1E5E55EEDDF3}">
       <text>
         <r>
           <rPr>
@@ -127,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="188">
   <si>
     <t>需求进度管理表</t>
   </si>
@@ -504,9 +489,6 @@
     <t>用户账户</t>
   </si>
   <si>
-    <t>手机号登录与自动注册</t>
-  </si>
-  <si>
     <t>个人信息展示</t>
   </si>
   <si>
@@ -765,13 +747,6 @@
 输入：目标用户ID及冻结或解冻操作。
 处理过程：校验当前状态后更新用户状态并记录操作；被冻结用户不得继续登录或发起新的充电业务。
 输出：显示操作结果和最新用户状态。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>前置条件：用户端程序正常运行且已连接服务端。
-输入：11位大陆手机号1[3-9][0-9]{9}。
-处理过程：客户端先判断手机号格式是否正确，再把手机号发给服务端；服务端查询用户表，如果已有该手机号就直接返回用户信息，如果没有就自动新增一条用户记录，默认昵称设为“用户+手机号后4位”。
-输出：登录成功后进入用户端首页，手机号格式错误或服务端连接失败时给出提示。</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
@@ -852,6 +827,29 @@
 输入：充值金额。充值金额必须为大于0的数字，最多保留两位小数。
 处理过程：用户输入充值金额并确认后，客户端先校验金额是否为空、是否为数字以及是否大于0；校验通过后将充值请求发送至服务端。服务端模拟支付成功，将充值金额加到当前用户的钱包余额中并保存。为避免重复充值，服务端对同一次充值请求只处理一次。
 输出：充值成功后显示充值金额和最新钱包余额；输入不符合要求时不发送充值请求并提示“请输入正确的充值金额”；服务端连接失败或数据库保存失败时，提示充值失败，用户余额保持不变。</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>手机号登录</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户注册</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴洵</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户输入用户名、手机号、密码进行账号注册</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>前置条件：用户端程序正常运行且已连接服务端。
+输入：11位大陆手机号1[3-9][0-9]{9}。
+处理过程：客户端先判断手机号格式是否正确，再把手机号发给服务端；服务端查询用户表，如果已有该手机号就直接返回用户信息，如果没有就提示”该用户不存在”。
+输出：登录成功后进入用户端首页，手机号格式错误或服务端连接失败时给出提示。</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1026,7 +1024,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1046,6 +1044,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1266,7 +1270,7 @@
     <xf numFmtId="181" fontId="22" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="16" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="16" applyFont="1" applyAlignment="1">
@@ -1369,6 +1373,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" xfId="28" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="29">
@@ -1522,7 +1529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IW161"/>
+  <dimension ref="A1:IW162"/>
   <sheetFormatPr defaultColWidth="10.21875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="1.88671875" style="1" customWidth="1"/>
@@ -1579,7 +1586,7 @@
         <v>7</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I3" s="30" t="s">
         <v>9</v>
@@ -1605,7 +1612,7 @@
         <v>71</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H4" s="25">
         <v>46269</v>
@@ -1628,7 +1635,7 @@
         <v>74</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H5" s="25">
         <v>46269</v>
@@ -1653,7 +1660,7 @@
         <v>77</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H6" s="25">
         <v>46269</v>
@@ -1676,7 +1683,7 @@
         <v>79</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H7" s="25">
         <v>46269</v>
@@ -1699,7 +1706,7 @@
         <v>81</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H8" s="25">
         <v>46269</v>
@@ -1720,13 +1727,13 @@
         <v>83</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H9" s="25">
         <v>46270</v>
@@ -1736,20 +1743,20 @@
       </c>
       <c r="J9" s="26"/>
     </row>
-    <row r="10" spans="2:10" ht="34.049999999999997" customHeight="1">
+    <row r="10" spans="2:10" ht="30" customHeight="1">
       <c r="B10" s="26">
         <v>7</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
       <c r="E10" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>86</v>
+        <v>184</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>186</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H10" s="25">
         <v>46270</v>
@@ -1766,13 +1773,13 @@
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
       <c r="E11" s="27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H11" s="25">
         <v>46270</v>
@@ -1789,13 +1796,13 @@
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
       <c r="E12" s="27" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H12" s="25">
         <v>46270</v>
@@ -1812,13 +1819,13 @@
       <c r="C13" s="27"/>
       <c r="D13" s="27"/>
       <c r="E13" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>184</v>
+        <v>88</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>89</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H13" s="25">
         <v>46270</v>
@@ -1833,40 +1840,40 @@
         <v>11</v>
       </c>
       <c r="C14" s="27"/>
-      <c r="D14" s="27" t="s">
-        <v>92</v>
-      </c>
+      <c r="D14" s="27"/>
       <c r="E14" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>182</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H14" s="25">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="I14" s="26" t="s">
         <v>72</v>
       </c>
       <c r="J14" s="26"/>
     </row>
-    <row r="15" spans="2:10" ht="82.05" customHeight="1">
+    <row r="15" spans="2:10" ht="34.049999999999997" customHeight="1">
       <c r="B15" s="26">
         <v>12</v>
       </c>
       <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
+      <c r="D15" s="27" t="s">
+        <v>91</v>
+      </c>
       <c r="E15" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>164</v>
+        <v>92</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>93</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H15" s="25">
         <v>46271</v>
@@ -1876,20 +1883,20 @@
       </c>
       <c r="J15" s="26"/>
     </row>
-    <row r="16" spans="2:10" ht="34.049999999999997" customHeight="1">
+    <row r="16" spans="2:10" ht="82.05" customHeight="1">
       <c r="B16" s="26">
         <v>13</v>
       </c>
       <c r="C16" s="27"/>
       <c r="D16" s="27"/>
       <c r="E16" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>97</v>
+        <v>94</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>163</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H16" s="25">
         <v>46271</v>
@@ -1899,47 +1906,45 @@
       </c>
       <c r="J16" s="26"/>
     </row>
-    <row r="17" spans="2:10" ht="82.05" customHeight="1">
+    <row r="17" spans="2:10" ht="34.049999999999997" customHeight="1">
       <c r="B17" s="26">
         <v>14</v>
       </c>
       <c r="C17" s="27"/>
-      <c r="D17" s="27" t="s">
-        <v>98</v>
-      </c>
+      <c r="D17" s="27"/>
       <c r="E17" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>171</v>
+        <v>95</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>96</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H17" s="25">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>72</v>
       </c>
       <c r="J17" s="26"/>
     </row>
-    <row r="18" spans="2:10" ht="34.049999999999997" customHeight="1">
+    <row r="18" spans="2:10" ht="82.05" customHeight="1">
       <c r="B18" s="26">
         <v>15</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>169</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H18" s="25">
         <v>46272</v>
@@ -1949,20 +1954,22 @@
       </c>
       <c r="J18" s="26"/>
     </row>
-    <row r="19" spans="2:10" ht="109.5" customHeight="1">
+    <row r="19" spans="2:10" ht="34.049999999999997" customHeight="1">
       <c r="B19" s="26">
         <v>16</v>
       </c>
       <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
+      <c r="D19" s="27" t="s">
+        <v>99</v>
+      </c>
       <c r="E19" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>183</v>
+        <v>100</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>101</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H19" s="25">
         <v>46272</v>
@@ -1972,20 +1979,20 @@
       </c>
       <c r="J19" s="26"/>
     </row>
-    <row r="20" spans="2:10" ht="34.049999999999997" customHeight="1">
+    <row r="20" spans="2:10" ht="109.5" customHeight="1">
       <c r="B20" s="26">
         <v>17</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="27"/>
       <c r="E20" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="28" t="s">
-        <v>104</v>
+        <v>168</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>181</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H20" s="25">
         <v>46272</v>
@@ -2002,40 +2009,36 @@
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
       <c r="E21" s="27" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H21" s="25">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="I21" s="26" t="s">
         <v>72</v>
       </c>
       <c r="J21" s="26"/>
     </row>
-    <row r="22" spans="2:10" ht="82.05" customHeight="1">
+    <row r="22" spans="2:10" ht="34.049999999999997" customHeight="1">
       <c r="B22" s="26">
         <v>19</v>
       </c>
-      <c r="C22" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>108</v>
-      </c>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
       <c r="E22" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" s="31" t="s">
-        <v>169</v>
+        <v>104</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>105</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H22" s="25">
         <v>46273</v>
@@ -2045,22 +2048,24 @@
       </c>
       <c r="J22" s="26"/>
     </row>
-    <row r="23" spans="2:10" ht="34.049999999999997" customHeight="1">
+    <row r="23" spans="2:10" ht="82.05" customHeight="1">
       <c r="B23" s="26">
         <v>20</v>
       </c>
-      <c r="C23" s="27"/>
+      <c r="C23" s="27" t="s">
+        <v>106</v>
+      </c>
       <c r="D23" s="27" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>112</v>
+        <v>108</v>
+      </c>
+      <c r="F23" s="31" t="s">
+        <v>167</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H23" s="25">
         <v>46273</v>
@@ -2070,20 +2075,22 @@
       </c>
       <c r="J23" s="26"/>
     </row>
-    <row r="24" spans="2:10" ht="82.05" customHeight="1">
+    <row r="24" spans="2:10" ht="34.049999999999997" customHeight="1">
       <c r="B24" s="26">
         <v>21</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27" t="s">
+        <v>109</v>
+      </c>
       <c r="E24" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" s="31" t="s">
-        <v>168</v>
+        <v>110</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>111</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H24" s="25">
         <v>46273</v>
@@ -2093,25 +2100,23 @@
       </c>
       <c r="J24" s="26"/>
     </row>
-    <row r="25" spans="2:10" ht="34.049999999999997" customHeight="1">
+    <row r="25" spans="2:10" ht="82.05" customHeight="1">
       <c r="B25" s="26">
         <v>22</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27" t="s">
-        <v>114</v>
-      </c>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
       <c r="E25" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>116</v>
+        <v>112</v>
+      </c>
+      <c r="F25" s="31" t="s">
+        <v>166</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H25" s="25">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="I25" s="26" t="s">
         <v>72</v>
@@ -2124,16 +2129,16 @@
       </c>
       <c r="C26" s="27"/>
       <c r="D26" s="27" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H26" s="25">
         <v>46274</v>
@@ -2143,20 +2148,22 @@
       </c>
       <c r="J26" s="26"/>
     </row>
-    <row r="27" spans="2:10" ht="82.05" customHeight="1">
+    <row r="27" spans="2:10" ht="34.049999999999997" customHeight="1">
       <c r="B27" s="26">
         <v>24</v>
       </c>
       <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
+      <c r="D27" s="27" t="s">
+        <v>116</v>
+      </c>
       <c r="E27" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="F27" s="31" t="s">
-        <v>165</v>
+        <v>117</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>118</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H27" s="25">
         <v>46274</v>
@@ -2166,25 +2173,23 @@
       </c>
       <c r="J27" s="26"/>
     </row>
-    <row r="28" spans="2:10" ht="34.049999999999997" customHeight="1">
+    <row r="28" spans="2:10" ht="82.05" customHeight="1">
       <c r="B28" s="26">
         <v>25</v>
       </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>123</v>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>164</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="H28" s="32">
-        <v>46275</v>
+        <v>178</v>
+      </c>
+      <c r="H28" s="25">
+        <v>46274</v>
       </c>
       <c r="I28" s="26" t="s">
         <v>72</v>
@@ -2196,15 +2201,17 @@
         <v>26</v>
       </c>
       <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
+      <c r="D29" s="26" t="s">
+        <v>120</v>
+      </c>
       <c r="E29" s="26" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H29" s="32">
         <v>46275</v>
@@ -2214,20 +2221,20 @@
       </c>
       <c r="J29" s="26"/>
     </row>
-    <row r="30" spans="2:10" ht="82.05" customHeight="1">
+    <row r="30" spans="2:10" ht="34.049999999999997" customHeight="1">
       <c r="B30" s="26">
         <v>27</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
       <c r="E30" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>127</v>
+        <v>123</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>124</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H30" s="32">
         <v>46275</v>
@@ -2237,22 +2244,20 @@
       </c>
       <c r="J30" s="26"/>
     </row>
-    <row r="31" spans="2:10" ht="34.049999999999997" customHeight="1">
+    <row r="31" spans="2:10" ht="82.05" customHeight="1">
       <c r="B31" s="26">
         <v>28</v>
       </c>
       <c r="C31" s="26"/>
-      <c r="D31" s="26" t="s">
-        <v>128</v>
-      </c>
+      <c r="D31" s="26"/>
       <c r="E31" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>130</v>
+        <v>125</v>
+      </c>
+      <c r="F31" s="31" t="s">
+        <v>126</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H31" s="32">
         <v>46275</v>
@@ -2262,47 +2267,45 @@
       </c>
       <c r="J31" s="26"/>
     </row>
-    <row r="32" spans="2:10" ht="82.05" customHeight="1">
+    <row r="32" spans="2:10" ht="34.049999999999997" customHeight="1">
       <c r="B32" s="26">
         <v>29</v>
       </c>
       <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
+      <c r="D32" s="26" t="s">
+        <v>127</v>
+      </c>
       <c r="E32" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="F32" s="31" t="s">
-        <v>166</v>
+        <v>128</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>129</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H32" s="32">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="I32" s="26" t="s">
         <v>72</v>
       </c>
       <c r="J32" s="26"/>
     </row>
-    <row r="33" spans="2:10" ht="34.049999999999997" customHeight="1">
+    <row r="33" spans="2:10" ht="82.05" customHeight="1">
       <c r="B33" s="26">
         <v>30</v>
       </c>
-      <c r="C33" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>133</v>
-      </c>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
       <c r="E33" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="F33" s="28" t="s">
-        <v>135</v>
+        <v>130</v>
+      </c>
+      <c r="F33" s="31" t="s">
+        <v>165</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H33" s="32">
         <v>46276</v>
@@ -2316,16 +2319,20 @@
       <c r="B34" s="26">
         <v>31</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
+      <c r="C34" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>132</v>
+      </c>
       <c r="E34" s="26" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H34" s="32">
         <v>46276</v>
@@ -2342,13 +2349,13 @@
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
       <c r="E35" s="26" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H35" s="32">
         <v>46276</v>
@@ -2365,16 +2372,16 @@
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
       <c r="E36" s="26" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H36" s="32">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="I36" s="26" t="s">
         <v>72</v>
@@ -2388,13 +2395,13 @@
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
       <c r="E37" s="26" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H37" s="32">
         <v>46277</v>
@@ -2409,17 +2416,15 @@
         <v>35</v>
       </c>
       <c r="C38" s="26"/>
-      <c r="D38" s="26" t="s">
-        <v>144</v>
-      </c>
+      <c r="D38" s="26"/>
       <c r="E38" s="26" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G38" s="26" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H38" s="32">
         <v>46277</v>
@@ -2434,18 +2439,20 @@
         <v>36</v>
       </c>
       <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
+      <c r="D39" s="26" t="s">
+        <v>143</v>
+      </c>
       <c r="E39" s="26" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G39" s="26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H39" s="32">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="I39" s="26" t="s">
         <v>72</v>
@@ -2457,17 +2464,15 @@
         <v>37</v>
       </c>
       <c r="C40" s="26"/>
-      <c r="D40" s="26" t="s">
-        <v>149</v>
-      </c>
+      <c r="D40" s="26"/>
       <c r="E40" s="26" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G40" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H40" s="32">
         <v>46278</v>
@@ -2481,23 +2486,21 @@
       <c r="B41" s="26">
         <v>38</v>
       </c>
-      <c r="C41" s="26" t="s">
-        <v>152</v>
-      </c>
+      <c r="C41" s="26"/>
       <c r="D41" s="26" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G41" s="26" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H41" s="32">
-        <v>46280</v>
+        <v>46278</v>
       </c>
       <c r="I41" s="26" t="s">
         <v>72</v>
@@ -2508,16 +2511,20 @@
       <c r="B42" s="26">
         <v>39</v>
       </c>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
+      <c r="C42" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>152</v>
+      </c>
       <c r="E42" s="26" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H42" s="32">
         <v>46280</v>
@@ -2532,20 +2539,18 @@
         <v>40</v>
       </c>
       <c r="C43" s="26"/>
-      <c r="D43" s="26" t="s">
-        <v>158</v>
-      </c>
+      <c r="D43" s="26"/>
       <c r="E43" s="26" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G43" s="26" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H43" s="32">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="I43" s="26" t="s">
         <v>72</v>
@@ -2558,16 +2563,16 @@
       </c>
       <c r="C44" s="26"/>
       <c r="D44" s="26" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F44" s="28" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G44" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H44" s="32">
         <v>46281</v>
@@ -2577,12 +2582,34 @@
       </c>
       <c r="J44" s="26"/>
     </row>
-    <row r="45" spans="2:10">
-      <c r="B45" s="20"/>
-      <c r="H45" s="33"/>
+    <row r="45" spans="2:10" ht="34.049999999999997" customHeight="1">
+      <c r="B45" s="26">
+        <v>42</v>
+      </c>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E45" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="G45" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="H45" s="32">
+        <v>46281</v>
+      </c>
+      <c r="I45" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="J45" s="26"/>
     </row>
     <row r="46" spans="2:10">
       <c r="B46" s="20"/>
+      <c r="H46" s="33"/>
     </row>
     <row r="47" spans="2:10">
       <c r="B47" s="20"/>
@@ -2928,6 +2955,9 @@
     </row>
     <row r="161" spans="2:2">
       <c r="B161" s="20"/>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/01需求矩阵-第4组-徐钲.xlsx
+++ b/01需求矩阵-第4组-徐钲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AAAnaughty rabbit\course\大三上\实训\Gale-Verdict-software-developing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CBB91F-011D-49EA-9241-3D5F935ED857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181BA03F-58F9-415B-BFEF-5D864AA48160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="192">
   <si>
     <t>需求进度管理表</t>
   </si>
@@ -852,6 +852,61 @@
 输出：登录成功后进入用户端首页，手机号格式错误或服务端连接失败时给出提示。</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○：完成（通过评审或测试）   △：进行中   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：未着手   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>N/A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t>：不适用（没有此项活动）</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>△</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>徐钲</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -870,7 +925,7 @@
     <numFmt numFmtId="181" formatCode="_(\\* #,##0_);_(\\* \(#,##0\);_(\\* \-_);_(@_)"/>
     <numFmt numFmtId="182" formatCode="[$-409]m/d/yyyy"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1021,6 +1076,12 @@
       <color indexed="81"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Noto Sans"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1270,7 +1331,7 @@
     <xf numFmtId="181" fontId="22" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="16" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="16" applyFont="1" applyAlignment="1">
@@ -1376,6 +1437,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="12" xfId="28" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="16" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="29">
@@ -1558,8 +1622,8 @@
       <c r="J1" s="29"/>
     </row>
     <row r="2" spans="2:10" ht="21" customHeight="1">
-      <c r="B2" s="35" t="s">
-        <v>1</v>
+      <c r="B2" s="38" t="s">
+        <v>188</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -1618,7 +1682,7 @@
         <v>46269</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J4" s="26"/>
     </row>
@@ -1641,7 +1705,7 @@
         <v>46269</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J5" s="26"/>
     </row>
@@ -1666,7 +1730,7 @@
         <v>46269</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J6" s="26"/>
     </row>
@@ -1689,7 +1753,7 @@
         <v>46269</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J7" s="26"/>
     </row>
@@ -1712,7 +1776,7 @@
         <v>46269</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J8" s="26"/>
     </row>
@@ -1733,13 +1797,13 @@
         <v>187</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H9" s="25">
         <v>46270</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="J9" s="26"/>
     </row>
@@ -1756,13 +1820,13 @@
         <v>186</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H10" s="25">
         <v>46270</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="J10" s="26"/>
     </row>
@@ -1779,13 +1843,13 @@
         <v>85</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="H11" s="25">
         <v>46270</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="J11" s="26"/>
     </row>
@@ -1802,13 +1866,13 @@
         <v>87</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="H12" s="25">
         <v>46270</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J12" s="26"/>
     </row>
@@ -1825,13 +1889,13 @@
         <v>89</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="H13" s="25">
         <v>46270</v>
       </c>
       <c r="I13" s="26" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="J13" s="26"/>
     </row>
@@ -1848,13 +1912,13 @@
         <v>182</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="H14" s="25">
         <v>46270</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="J14" s="26"/>
     </row>
@@ -1879,7 +1943,7 @@
         <v>46271</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="J15" s="26"/>
     </row>
@@ -1902,7 +1966,7 @@
         <v>46271</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="J16" s="26"/>
     </row>
@@ -1925,7 +1989,7 @@
         <v>46271</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J17" s="26"/>
     </row>
@@ -1950,7 +2014,7 @@
         <v>46272</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J18" s="26"/>
     </row>
@@ -1975,7 +2039,7 @@
         <v>46272</v>
       </c>
       <c r="I19" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J19" s="26"/>
     </row>
@@ -1998,7 +2062,7 @@
         <v>46272</v>
       </c>
       <c r="I20" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J20" s="26"/>
     </row>
@@ -2021,7 +2085,7 @@
         <v>46272</v>
       </c>
       <c r="I21" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J21" s="26"/>
     </row>
@@ -2044,7 +2108,7 @@
         <v>46273</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J22" s="26"/>
     </row>
@@ -2071,7 +2135,7 @@
         <v>46273</v>
       </c>
       <c r="I23" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J23" s="26"/>
     </row>
@@ -2096,7 +2160,7 @@
         <v>46273</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J24" s="26"/>
     </row>
@@ -2119,7 +2183,7 @@
         <v>46273</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J25" s="26"/>
     </row>
@@ -2138,13 +2202,13 @@
         <v>115</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="H26" s="25">
         <v>46274</v>
       </c>
       <c r="I26" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J26" s="26"/>
     </row>
@@ -2163,13 +2227,13 @@
         <v>118</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="H27" s="25">
         <v>46274</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J27" s="26"/>
     </row>
@@ -2186,13 +2250,13 @@
         <v>164</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="H28" s="25">
         <v>46274</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J28" s="26"/>
     </row>
@@ -2217,7 +2281,7 @@
         <v>46275</v>
       </c>
       <c r="I29" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J29" s="26"/>
     </row>
@@ -2240,7 +2304,7 @@
         <v>46275</v>
       </c>
       <c r="I30" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J30" s="26"/>
     </row>
@@ -2263,7 +2327,7 @@
         <v>46275</v>
       </c>
       <c r="I31" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J31" s="26"/>
     </row>
@@ -2288,7 +2352,7 @@
         <v>46275</v>
       </c>
       <c r="I32" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J32" s="26"/>
     </row>
@@ -2311,7 +2375,7 @@
         <v>46276</v>
       </c>
       <c r="I33" s="26" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="J33" s="26"/>
     </row>
@@ -2338,7 +2402,7 @@
         <v>46276</v>
       </c>
       <c r="I34" s="26" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="J34" s="26"/>
     </row>

--- a/01需求矩阵-第4组-徐钲.xlsx
+++ b/01需求矩阵-第4组-徐钲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AAAnaughty rabbit\course\大三上\实训\Gale-Verdict-software-developing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181BA03F-58F9-415B-BFEF-5D864AA48160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A14062D-6F1B-4FD3-879F-C5911104B70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -846,13 +846,6 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>前置条件：用户端程序正常运行且已连接服务端。
-输入：11位大陆手机号1[3-9][0-9]{9}。
-处理过程：客户端先判断手机号格式是否正确，再把手机号发给服务端；服务端查询用户表，如果已有该手机号就直接返回用户信息，如果没有就提示”该用户不存在”。
-输出：登录成功后进入用户端首页，手机号格式错误或服务端连接失败时给出提示。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -905,6 +898,13 @@
   </si>
   <si>
     <t>徐钲</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>前置条件：用户端程序正常运行且已连接服务端。
+输入：11位大陆手机号1[3-9][0-9]{9}或用户名，密码。
+处理过程：客户端先判断手机号或用户格式是否正确，再把手机号或用户名发给服务端；服务端查询用户表，如果已有该手机号或用户就直接返回用户信息，如果没有就提示”该用户不存在”。
+输出：登录成功后进入用户端首页，手机号格式错误或服务端连接失败时给出提示。</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1426,19 +1426,19 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" xfId="28" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="28" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="16" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" xfId="28" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="16" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1609,26 +1609,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="41.25" customHeight="1">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="29"/>
       <c r="H1" s="29"/>
       <c r="I1" s="29"/>
       <c r="J1" s="29"/>
     </row>
     <row r="2" spans="2:10" ht="21" customHeight="1">
-      <c r="B2" s="38" t="s">
-        <v>188</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="B2" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B3" s="30" t="s">
@@ -1682,7 +1682,7 @@
         <v>46269</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J4" s="26"/>
     </row>
@@ -1705,7 +1705,7 @@
         <v>46269</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J5" s="26"/>
     </row>
@@ -1730,7 +1730,7 @@
         <v>46269</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J6" s="26"/>
     </row>
@@ -1753,7 +1753,7 @@
         <v>46269</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J7" s="26"/>
     </row>
@@ -1776,7 +1776,7 @@
         <v>46269</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J8" s="26"/>
     </row>
@@ -1794,7 +1794,7 @@
         <v>183</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G9" s="26" t="s">
         <v>171</v>
@@ -1803,7 +1803,7 @@
         <v>46270</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J9" s="26"/>
     </row>
@@ -1816,17 +1816,17 @@
       <c r="E10" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="34" t="s">
         <v>186</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H10" s="25">
         <v>46270</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J10" s="26"/>
     </row>
@@ -1843,13 +1843,13 @@
         <v>85</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H11" s="25">
         <v>46270</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J11" s="26"/>
     </row>
@@ -1866,13 +1866,13 @@
         <v>87</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H12" s="25">
         <v>46270</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J12" s="26"/>
     </row>
@@ -1889,13 +1889,13 @@
         <v>89</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H13" s="25">
         <v>46270</v>
       </c>
       <c r="I13" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J13" s="26"/>
     </row>
@@ -1912,13 +1912,13 @@
         <v>182</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H14" s="25">
         <v>46270</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J14" s="26"/>
     </row>
@@ -1943,7 +1943,7 @@
         <v>46271</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J15" s="26"/>
     </row>
@@ -1966,7 +1966,7 @@
         <v>46271</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J16" s="26"/>
     </row>
@@ -1989,7 +1989,7 @@
         <v>46271</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J17" s="26"/>
     </row>
@@ -2014,7 +2014,7 @@
         <v>46272</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J18" s="26"/>
     </row>
@@ -2039,7 +2039,7 @@
         <v>46272</v>
       </c>
       <c r="I19" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J19" s="26"/>
     </row>
@@ -2062,7 +2062,7 @@
         <v>46272</v>
       </c>
       <c r="I20" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J20" s="26"/>
     </row>
@@ -2085,7 +2085,7 @@
         <v>46272</v>
       </c>
       <c r="I21" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J21" s="26"/>
     </row>
@@ -2108,7 +2108,7 @@
         <v>46273</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J22" s="26"/>
     </row>
@@ -2135,7 +2135,7 @@
         <v>46273</v>
       </c>
       <c r="I23" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J23" s="26"/>
     </row>
@@ -2160,7 +2160,7 @@
         <v>46273</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J24" s="26"/>
     </row>
@@ -2183,7 +2183,7 @@
         <v>46273</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J25" s="26"/>
     </row>
@@ -2208,7 +2208,7 @@
         <v>46274</v>
       </c>
       <c r="I26" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J26" s="26"/>
     </row>
@@ -2233,7 +2233,7 @@
         <v>46274</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J27" s="26"/>
     </row>
@@ -2256,7 +2256,7 @@
         <v>46274</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J28" s="26"/>
     </row>
@@ -2281,7 +2281,7 @@
         <v>46275</v>
       </c>
       <c r="I29" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J29" s="26"/>
     </row>
@@ -2304,7 +2304,7 @@
         <v>46275</v>
       </c>
       <c r="I30" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J30" s="26"/>
     </row>
@@ -2327,7 +2327,7 @@
         <v>46275</v>
       </c>
       <c r="I31" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J31" s="26"/>
     </row>
@@ -2352,7 +2352,7 @@
         <v>46275</v>
       </c>
       <c r="I32" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J32" s="26"/>
     </row>
@@ -2375,7 +2375,7 @@
         <v>46276</v>
       </c>
       <c r="I33" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J33" s="26"/>
     </row>
@@ -2402,7 +2402,7 @@
         <v>46276</v>
       </c>
       <c r="I34" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J34" s="26"/>
     </row>
@@ -3053,22 +3053,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="41.25" customHeight="1">
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="2" spans="2:12" ht="21" customHeight="1">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1">
       <c r="B3" s="5" t="s">
